--- a/database/seeds/sources/staff.xlsx
+++ b/database/seeds/sources/staff.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3465" uniqueCount="2089">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="2147">
   <si>
     <t xml:space="preserve">ПЧ</t>
   </si>
@@ -187,6 +187,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель сотрудник</t>
     </r>
@@ -195,6 +196,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант</t>
     </r>
@@ -218,6 +220,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель сотрудник</t>
     </r>
@@ -226,6 +229,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> прапорщик</t>
     </r>
@@ -248,6 +252,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель сотрудник</t>
     </r>
@@ -257,6 +262,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.сержант</t>
     </r>
@@ -292,6 +298,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный</t>
     </r>
@@ -301,6 +308,7 @@
         <sz val="12"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -310,6 +318,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мл.сержант</t>
     </r>
@@ -354,6 +363,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный</t>
     </r>
@@ -362,6 +372,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл.сержант</t>
     </r>
@@ -448,6 +459,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Р/телефонистка</t>
     </r>
@@ -456,6 +468,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">  сержант</t>
     </r>
@@ -473,6 +486,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Р/телефонистка</t>
     </r>
@@ -481,6 +495,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> старшина</t>
     </r>
@@ -498,6 +513,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Р/телефонистка</t>
     </r>
@@ -506,6 +522,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант</t>
     </r>
@@ -515,6 +532,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст. сержант</t>
     </r>
@@ -532,6 +550,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Р</t>
     </r>
@@ -540,6 +559,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">/телефонистка мл.сержант</t>
     </r>
@@ -554,6 +574,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Майлыбаев </t>
     </r>
@@ -562,6 +583,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">А</t>
     </r>
@@ -571,6 +593,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">скар Нургазиевич</t>
     </r>
@@ -581,6 +604,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Н</t>
     </r>
@@ -589,6 +613,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ачальник части</t>
     </r>
@@ -597,6 +622,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Капитан г/з</t>
     </r>
@@ -613,6 +639,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Начальник караула</t>
     </r>
@@ -621,6 +648,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Ст. лейтенант г/з</t>
     </r>
@@ -643,6 +671,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Начальник караула</t>
     </r>
@@ -651,6 +680,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> лейтенант</t>
     </r>
@@ -659,6 +689,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> г/з</t>
     </r>
@@ -681,6 +712,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения Ст</t>
     </r>
@@ -689,6 +721,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">арший </t>
     </r>
@@ -697,6 +730,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -705,6 +739,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> г/з</t>
     </r>
@@ -721,6 +756,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения Сержант </t>
     </r>
@@ -729,6 +765,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г/з</t>
     </r>
@@ -751,6 +788,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения</t>
     </r>
@@ -759,6 +797,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Сержант  г/з</t>
     </r>
@@ -805,6 +844,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Вод</t>
     </r>
@@ -813,6 +853,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -821,6 +862,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> – сотрудник</t>
     </r>
@@ -829,6 +871,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант г/з</t>
     </r>
@@ -845,6 +888,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Вод</t>
     </r>
@@ -853,6 +897,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -861,6 +906,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> – сотрудник Прапорщик</t>
     </r>
@@ -869,6 +915,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> г/з</t>
     </r>
@@ -885,6 +932,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Вод</t>
     </r>
@@ -893,6 +941,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -901,6 +950,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> – сотрудник</t>
     </r>
@@ -909,6 +959,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Младший сержант  г/з</t>
     </r>
@@ -925,6 +976,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Вод</t>
     </r>
@@ -933,6 +985,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -941,6 +994,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> – сотрудник Ст</t>
     </r>
@@ -949,6 +1003,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">арший </t>
     </r>
@@ -957,6 +1012,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -965,6 +1021,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman KZ"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> г/з</t>
     </r>
@@ -1116,6 +1173,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Авашев Арвахун Майдынович</t>
     </r>
@@ -1125,6 +1183,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1171,6 +1230,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Батык</t>
     </r>
@@ -1180,6 +1240,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">уулу </t>
     </r>
@@ -1188,6 +1249,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Азамат</t>
     </r>
@@ -1231,6 +1293,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Курманбеков Арслан Жолдасбек</t>
     </r>
@@ -1240,6 +1303,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -1248,6 +1312,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лы  </t>
     </r>
@@ -1264,6 +1329,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Т</t>
     </r>
@@ -1273,6 +1339,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ө</t>
     </r>
@@ -1281,6 +1348,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лек Жандос Аскар</t>
     </r>
@@ -1290,6 +1358,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -1298,6 +1367,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лы</t>
     </r>
@@ -1330,6 +1400,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Диқанбай Исатай Әкімханұлы</t>
     </r>
@@ -1338,6 +1409,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">   </t>
     </r>
@@ -1357,6 +1429,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ес</t>
     </r>
@@ -1366,6 +1439,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">і</t>
     </r>
@@ -1374,6 +1448,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ркепов Ернат Ер</t>
     </r>
@@ -1383,6 +1458,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ғ</t>
     </r>
@@ -1391,6 +1467,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">али</t>
     </r>
@@ -1400,6 +1477,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұлы</t>
     </r>
@@ -1458,6 +1536,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Вр.и.о. Г/К</t>
     </r>
@@ -1467,6 +1546,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> вольнонаемный</t>
     </r>
@@ -1480,6 +1560,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Техник части</t>
     </r>
@@ -1489,6 +1570,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> вольнонаемный</t>
     </r>
@@ -1606,6 +1688,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель</t>
     </r>
@@ -1614,6 +1697,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-</t>
     </r>
@@ -1622,6 +1706,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сотрудник</t>
     </r>
@@ -1630,6 +1715,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> старшина
 </t>
@@ -1647,6 +1733,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель</t>
     </r>
@@ -1655,6 +1742,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-</t>
     </r>
@@ -1663,6 +1751,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сотрудник</t>
     </r>
@@ -1671,6 +1760,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант</t>
     </r>
@@ -1684,6 +1774,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -1692,6 +1783,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">21.08.1994
 </t>
@@ -1701,6 +1793,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">
 </t>
@@ -1801,6 +1894,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель</t>
     </r>
@@ -1809,6 +1903,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-</t>
     </r>
@@ -1817,6 +1912,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сотрудник</t>
     </r>
@@ -1825,6 +1921,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> младший сержант</t>
     </r>
@@ -1868,6 +1965,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ер</t>
     </r>
@@ -1876,6 +1974,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">і</t>
     </r>
@@ -1884,6 +1983,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мханов
 Нуржан
@@ -1931,6 +2031,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель</t>
     </r>
@@ -1939,6 +2040,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-</t>
     </r>
@@ -1947,6 +2049,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сотрудник</t>
     </r>
@@ -1955,6 +2058,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> прапорщик</t>
     </r>
@@ -1965,6 +2069,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Меделхан
 Мейрамбек
@@ -1975,6 +2080,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұлы</t>
     </r>
@@ -2058,6 +2164,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сулейманов
 Руслан
@@ -2068,6 +2175,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -2076,6 +2184,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лы</t>
     </r>
@@ -2097,6 +2206,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель</t>
     </r>
@@ -2105,6 +2215,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-</t>
     </r>
@@ -2113,6 +2224,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сотрудник</t>
     </r>
@@ -2121,6 +2233,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> прапорщик
 </t>
@@ -2132,6 +2245,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ма</t>
     </r>
@@ -2140,6 +2254,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">қ</t>
     </r>
@@ -2148,6 +2263,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">анов
 Ж</t>
@@ -2157,6 +2273,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -2165,6 +2282,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мабек
 Есен</t>
@@ -2174,6 +2292,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ғазыұлы</t>
     </r>
@@ -2412,6 +2531,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2420,6 +2540,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарныймл.сержант г\з</t>
     </r>
@@ -2631,6 +2752,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">16</t>
     </r>
@@ -2639,6 +2761,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.07.19</t>
     </r>
@@ -2647,6 +2770,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">88</t>
     </r>
@@ -2666,6 +2790,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">прапорщик г/з, </t>
     </r>
@@ -2674,6 +2799,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.водитель</t>
     </r>
@@ -2732,6 +2858,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Толеген</t>
     </r>
@@ -2740,6 +2867,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -2748,6 +2876,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Азамат Кайратович</t>
     </r>
@@ -2917,6 +3046,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">10</t>
     </r>
@@ -2925,6 +3055,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.01.19</t>
     </r>
@@ -2933,6 +3064,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">93</t>
     </r>
@@ -2961,6 +3093,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старшина г/з, </t>
     </r>
@@ -2969,6 +3102,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель</t>
     </r>
@@ -2985,6 +3119,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">рядовой г/з, </t>
     </r>
@@ -2993,6 +3128,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель</t>
     </r>
@@ -3009,6 +3145,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.сержант г/з, </t>
     </r>
@@ -3017,6 +3154,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель</t>
     </r>
@@ -3042,6 +3180,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант г/з, </t>
     </r>
@@ -3050,6 +3189,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель</t>
     </r>
@@ -3075,6 +3215,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мл.сержант г/з, </t>
     </r>
@@ -3083,6 +3224,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель</t>
     </r>
@@ -3140,6 +3282,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">майор, заместитель  начальника части </t>
     </r>
@@ -3148,6 +3291,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">по В и СПР</t>
     </r>
@@ -3667,6 +3811,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">12.01.992</t>
     </r>
@@ -3675,6 +3820,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г</t>
     </r>
@@ -3689,6 +3835,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Усов Валерий</t>
     </r>
@@ -3697,6 +3844,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -3706,6 +3854,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Викторович</t>
     </r>
@@ -3734,6 +3883,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -3742,6 +3892,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">2</t>
     </r>
@@ -3750,6 +3901,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.0</t>
     </r>
@@ -3758,6 +3910,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">9</t>
     </r>
@@ -3766,6 +3919,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.198</t>
     </r>
@@ -3774,6 +3928,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
     </r>
@@ -3782,6 +3937,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г.</t>
     </r>
@@ -3855,6 +4011,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сержант</t>
     </r>
@@ -3863,6 +4020,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, </t>
     </r>
@@ -3871,6 +4029,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотрудник</t>
     </r>
@@ -3920,6 +4079,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Мл.сержант</t>
     </r>
@@ -3928,6 +4088,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">, пожарный</t>
     </r>
@@ -3936,6 +4097,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> спасатель</t>
     </r>
@@ -4587,6 +4749,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Зам начальник Капитан </t>
     </r>
@@ -4595,6 +4758,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр/ защиты</t>
     </r>
@@ -4608,6 +4772,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">24.10.</t>
     </r>
@@ -4616,6 +4781,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4624,6 +4790,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">74г.
 казах</t>
@@ -4635,6 +4802,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отеделения
 ст. сержант</t>
@@ -4645,6 +4813,7 @@
         <color rgb="FF00B050"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4653,6 +4822,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр/ защиты</t>
     </r>
@@ -4683,6 +4853,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отд. 
 Ст. сержант</t>
@@ -4693,6 +4864,7 @@
         <color rgb="FF00B050"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -4701,6 +4873,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр/ защиты</t>
     </r>
@@ -4718,6 +4891,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отд.
 Ст. сержант</t>
@@ -4727,6 +4901,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> гр/ защиты
 </t>
@@ -4741,6 +4916,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">16.03.</t>
     </r>
@@ -4749,6 +4925,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4757,6 +4934,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">80г.
 уйгур</t>
@@ -4768,6 +4946,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отд.
 старшина</t>
@@ -4777,6 +4956,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> гр/ защиты
 </t>
@@ -4791,6 +4971,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">14.05.</t>
     </r>
@@ -4799,6 +4980,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4807,6 +4989,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">83г.
 казах</t>
@@ -4818,6 +5001,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотр-к</t>
     </r>
@@ -4826,6 +5010,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -4835,6 +5020,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старшина гр/ защиты</t>
     </r>
@@ -4848,6 +5034,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">13.03.</t>
     </r>
@@ -4856,6 +5043,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4864,6 +5052,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">77г.
 казах</t>
@@ -4875,6 +5064,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотр-к</t>
     </r>
@@ -4883,6 +5073,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> старшина  гр/ защиты</t>
     </r>
@@ -4896,6 +5087,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">09.07.</t>
     </r>
@@ -4904,6 +5096,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4912,6 +5105,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">78г.
 казах</t>
@@ -4923,6 +5117,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотр-к</t>
     </r>
@@ -4931,6 +5126,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -4940,6 +5136,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Старшина  гр/ защиты</t>
     </r>
@@ -4953,6 +5150,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">21.03.</t>
     </r>
@@ -4961,6 +5159,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -4969,6 +5168,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">86г.
 казах</t>
@@ -4980,6 +5180,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотр-к</t>
     </r>
@@ -4988,6 +5189,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -4997,6 +5199,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст. сержант гр/ защиты</t>
     </r>
@@ -5039,6 +5242,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">01.11.</t>
     </r>
@@ -5047,6 +5251,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5055,6 +5260,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">80г.
 казах</t>
@@ -5066,6 +5272,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст. пожарный</t>
     </r>
@@ -5074,6 +5281,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -5083,6 +5291,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сержант гр/ защиты
 </t>
@@ -5106,6 +5315,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Окенов Ернар </t>
     </r>
@@ -5114,6 +5324,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Е</t>
     </r>
@@ -5122,6 +5333,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ржанович</t>
     </r>
@@ -5132,6 +5344,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">28.04.</t>
     </r>
@@ -5140,6 +5353,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5148,6 +5362,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">83г.
 казах</t>
@@ -5170,6 +5385,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст. пожарный</t>
     </r>
@@ -5178,6 +5394,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Сержант гр/ защиты
 </t>
@@ -5203,6 +5420,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">15.11.</t>
     </r>
@@ -5211,6 +5429,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5219,6 +5438,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">75г.
 казашка</t>
@@ -5238,6 +5458,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">30.11.</t>
     </r>
@@ -5246,6 +5467,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5254,6 +5476,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">76г.
 казашка</t>
@@ -5273,6 +5496,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">18.05.</t>
     </r>
@@ -5281,6 +5505,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5289,6 +5514,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">80г.
 уйгурка</t>
@@ -5309,6 +5535,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">16</t>
     </r>
@@ -5317,6 +5544,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.0</t>
     </r>
@@ -5325,6 +5553,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -5333,6 +5562,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -5341,6 +5571,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5349,6 +5580,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">9</t>
     </r>
@@ -5357,6 +5589,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -5365,6 +5598,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г.
 казах</t>
@@ -5384,6 +5618,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1</t>
     </r>
@@ -5392,6 +5627,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">3.0</t>
     </r>
@@ -5400,6 +5636,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">8</t>
     </r>
@@ -5408,6 +5645,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -5416,6 +5654,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1993</t>
     </r>
@@ -5424,6 +5663,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г.</t>
     </r>
@@ -5448,6 +5688,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">08.09.1990г</t>
     </r>
@@ -5457,6 +5698,7 @@
         <color rgb="FF00B050"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -5474,6 +5716,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Мл. инс. 
 гр. кадров</t>
@@ -5483,6 +5726,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Сержант гр/ защиты</t>
     </r>
@@ -5507,6 +5751,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">13.04.</t>
     </r>
@@ -5515,6 +5760,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1984</t>
     </r>
@@ -5523,6 +5769,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г.
 казах</t>
@@ -5534,6 +5781,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отд. </t>
     </r>
@@ -5542,6 +5790,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Старшина
 </t>
@@ -5551,6 +5800,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр/ защиты</t>
     </r>
@@ -5568,6 +5818,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст. пожарный</t>
     </r>
@@ -5576,6 +5827,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Старшина гр/ защиты</t>
     </r>
@@ -5589,6 +5841,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">19</t>
     </r>
@@ -5598,6 +5851,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">73</t>
     </r>
@@ -5608,6 +5862,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст. пожарный</t>
     </r>
@@ -5616,6 +5871,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.сержант гр/ защиты</t>
     </r>
@@ -5629,6 +5885,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ком. отд.
 Ст</t>
@@ -5638,6 +5895,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">аршина гр/ защиты</t>
     </r>
@@ -5683,6 +5941,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Заместитель начальника части по службе</t>
     </r>
@@ -5691,6 +5950,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> майор</t>
     </r>
@@ -5744,6 +6004,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Начальник караула</t>
     </r>
@@ -5752,6 +6013,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст. лейтенант</t>
     </r>
@@ -5813,6 +6075,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Командир отделения</t>
     </r>
@@ -5821,6 +6084,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.с</t>
     </r>
@@ -5829,6 +6093,7 @@
         <sz val="12"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ержант</t>
     </r>
@@ -6065,6 +6330,7 @@
         <color rgb="FF00000A"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ОспановАлимжан </t>
     </r>
@@ -6074,6 +6340,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Иминжанович</t>
     </r>
@@ -6096,6 +6363,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">И.о начальника части </t>
     </r>
@@ -6104,6 +6372,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст. лейтенант </t>
     </r>
@@ -6112,6 +6381,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> г/з</t>
     </r>
@@ -6179,6 +6449,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">К</t>
     </r>
@@ -6187,6 +6458,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -6195,6 +6467,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">са</t>
     </r>
@@ -6203,6 +6476,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">йы</t>
     </r>
@@ -6211,6 +6485,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">н Айшуа</t>
     </r>
@@ -6219,6 +6494,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">қ</t>
     </r>
@@ -6227,6 +6503,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Н</t>
     </r>
@@ -6235,6 +6512,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ү</t>
     </r>
@@ -6243,6 +6521,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">р</t>
     </r>
@@ -6251,6 +6530,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ә</t>
     </r>
@@ -6259,6 +6539,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ж</t>
     </r>
@@ -6267,6 +6548,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">іұ</t>
     </r>
@@ -6275,6 +6557,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лы</t>
     </r>
@@ -6348,6 +6631,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">К</t>
     </r>
@@ -6356,6 +6640,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">і</t>
     </r>
@@ -6364,6 +6649,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">р</t>
     </r>
@@ -6372,6 +6658,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">і</t>
     </r>
@@ -6380,6 +6667,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сбай Айбек Сейсенбай</t>
     </r>
@@ -6388,6 +6676,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұлы</t>
     </r>
@@ -6497,6 +6786,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0</t>
     </r>
@@ -6505,6 +6795,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">9</t>
     </r>
@@ -6513,6 +6804,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.0</t>
     </r>
@@ -6521,6 +6813,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">7</t>
     </r>
@@ -6529,6 +6822,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.1977</t>
     </r>
@@ -6548,6 +6842,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Турсунов Са</t>
     </r>
@@ -6556,6 +6851,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">й</t>
     </r>
@@ -6564,6 +6860,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">яр Мунарбекович</t>
     </r>
@@ -6724,6 +7021,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.</t>
     </r>
@@ -6732,6 +7030,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -6740,6 +7039,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант, старший пожарный</t>
     </r>
@@ -6786,6 +7086,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">С</t>
     </r>
@@ -6794,6 +7095,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ы</t>
     </r>
@@ -6802,6 +7104,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">дыкбаев Темиржан Серикович</t>
     </r>
@@ -6815,6 +7118,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сарсенбаева М</t>
     </r>
@@ -6823,6 +7127,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ө</t>
     </r>
@@ -6831,6 +7136,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лд</t>
     </r>
@@ -6839,6 +7145,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ір Ғабитқызы</t>
     </r>
@@ -6927,6 +7234,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Д</t>
     </r>
@@ -6935,6 +7243,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">әуенов Еламан Қамбарұлы</t>
     </r>
@@ -6990,6 +7299,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">К</t>
     </r>
@@ -6998,6 +7308,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">о</t>
     </r>
@@ -7006,6 +7317,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">бенкулов Нурлан Кежебекович</t>
     </r>
@@ -7058,6 +7370,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7066,6 +7379,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лейтенант, начальник караула</t>
     </r>
@@ -7154,6 +7468,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Рахимолиев</t>
     </r>
@@ -7162,6 +7477,7 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7170,6 +7486,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Бекжан</t>
     </r>
@@ -7178,6 +7495,7 @@
         <sz val="10"/>
         <rFont val="Calibri"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -7186,6 +7504,7 @@
         <sz val="10"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Айбекулы</t>
     </r>
@@ -7223,6 +7542,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст. </t>
     </r>
@@ -7231,6 +7551,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лейтенант начальник караула</t>
     </r>
@@ -7241,6 +7562,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ибрагимов Алишер </t>
     </r>
@@ -7249,6 +7571,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Мухамедович</t>
     </r>
@@ -7284,6 +7607,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сембаев </t>
     </r>
@@ -7292,6 +7616,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Серикбол Нурданович</t>
     </r>
@@ -7302,6 +7627,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">14</t>
     </r>
@@ -7310,6 +7636,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.05.1983</t>
     </r>
@@ -7320,6 +7647,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Заместитель начальника по службе</t>
     </r>
@@ -7328,6 +7656,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.лейтенант
 </t>
@@ -7337,6 +7666,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">г/з</t>
     </r>
@@ -7371,6 +7701,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">с</t>
     </r>
@@ -7379,6 +7710,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">тарший инженер</t>
     </r>
@@ -7387,6 +7719,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> лейтенант 
 </t>
@@ -7396,6 +7729,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -7412,6 +7746,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">к</t>
     </r>
@@ -7420,6 +7755,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ом</t>
     </r>
@@ -7428,6 +7764,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">андир </t>
     </r>
@@ -7436,6 +7773,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">отделения старшина
 гр.защиты</t>
@@ -7453,6 +7791,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения</t>
     </r>
@@ -7461,6 +7800,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.сержа</t>
     </r>
@@ -7469,6 +7809,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">нт
 гр.защиты</t>
@@ -7483,6 +7824,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">с</t>
     </r>
@@ -7491,6 +7833,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">т.</t>
     </r>
@@ -7499,6 +7842,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мастер ГДЗС</t>
     </r>
@@ -7507,6 +7851,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.сержант
 гр.защиты</t>
@@ -7547,6 +7892,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Әші</t>
     </r>
@@ -7555,6 +7901,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мов Орынбасар</t>
     </r>
@@ -7563,6 +7910,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Тәуіржанұлы</t>
     </r>
@@ -7595,6 +7943,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">радио-телефонист Ст.сержант</t>
     </r>
@@ -7603,6 +7952,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> гр.защиты</t>
     </r>
@@ -7616,6 +7966,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">09</t>
     </r>
@@ -7624,6 +7975,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.11.1994</t>
     </r>
@@ -7667,6 +8019,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный спасатель</t>
     </r>
@@ -7675,6 +8028,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> м</t>
     </r>
@@ -7683,6 +8037,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">л.сержант
 гр.защиты</t>
@@ -7700,6 +8055,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.
 </t>
@@ -7709,6 +8065,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по </t>
     </r>
@@ -7717,6 +8074,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">во</t>
     </r>
@@ -7725,6 +8083,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ждению ПА сержант гр.защиты</t>
     </r>
@@ -7738,6 +8097,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.
 </t>
@@ -7747,6 +8107,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по </t>
     </r>
@@ -7755,6 +8116,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">во</t>
     </r>
@@ -7763,6 +8125,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ждению ПА старшина гр.защиты</t>
     </r>
@@ -7833,6 +8196,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">к</t>
     </r>
@@ -7841,6 +8205,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">омандир отделения</t>
     </r>
@@ -7849,6 +8214,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> старшина
 </t>
@@ -7858,6 +8224,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -7874,6 +8241,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения сержа</t>
     </r>
@@ -7882,6 +8250,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">нт
 гр.защиты</t>
@@ -7908,6 +8277,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель-сотрудник</t>
     </r>
@@ -7916,6 +8286,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант
 </t>
@@ -7925,6 +8296,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -7951,6 +8323,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.п</t>
     </r>
@@ -7959,6 +8332,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ожарный-</t>
     </r>
@@ -7967,6 +8341,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">спасатель сержант
 </t>
@@ -7976,6 +8351,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -7998,6 +8374,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">п</t>
     </r>
@@ -8006,6 +8383,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ожарный-</t>
     </r>
@@ -8014,6 +8392,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">спасатель мл.сержант
 </t>
@@ -8023,6 +8402,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр. защиты</t>
     </r>
@@ -8040,6 +8420,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный-спасатель
  </t>
@@ -8049,6 +8430,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мл. сержант
 </t>
@@ -8058,6 +8440,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8074,6 +8457,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">р</t>
     </r>
@@ -8082,6 +8466,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">адио-телефонист</t>
     </r>
@@ -8090,6 +8475,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант
 </t>
@@ -8099,6 +8485,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8148,6 +8535,7 @@
         <color rgb="FF000000"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Иманбеков </t>
     </r>
@@ -8156,6 +8544,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Галым Ганиевич</t>
     </r>
@@ -8169,6 +8558,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старший
 инженер</t>
@@ -8178,6 +8568,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> майор гр.защиты</t>
     </r>
@@ -8194,6 +8585,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">к</t>
     </r>
@@ -8202,6 +8594,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">омандир отделения</t>
     </r>
@@ -8210,6 +8603,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> старшина </t>
     </r>
@@ -8218,6 +8612,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8234,6 +8629,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">к</t>
     </r>
@@ -8242,6 +8638,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">омандир отделения
 сержант гр.защиты</t>
@@ -8269,6 +8666,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.инструктор по </t>
     </r>
@@ -8277,6 +8675,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">во</t>
     </r>
@@ -8285,6 +8684,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ждению ПА старшина
 </t>
@@ -8294,6 +8694,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8363,6 +8764,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст.п</t>
     </r>
@@ -8371,6 +8773,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ожарный</t>
     </r>
@@ -8379,6 +8782,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-спасатель сержант </t>
     </r>
@@ -8387,6 +8791,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8397,6 +8802,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Аманбеков </t>
     </r>
@@ -8405,6 +8811,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Біржан Серікұлы</t>
     </r>
@@ -8415,6 +8822,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">30</t>
     </r>
@@ -8423,6 +8831,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.03.1996</t>
     </r>
@@ -8433,6 +8842,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный-спасатель</t>
     </r>
@@ -8441,6 +8851,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант </t>
     </r>
@@ -8449,6 +8860,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8465,6 +8877,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный-спасатель</t>
     </r>
@@ -8473,6 +8886,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл. сержант</t>
     </r>
@@ -8481,6 +8895,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8497,6 +8912,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.пожарный спасатель сержант </t>
     </r>
@@ -8505,6 +8921,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8521,6 +8938,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный
 </t>
@@ -8530,6 +8948,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">спасатель</t>
     </r>
@@ -8538,6 +8957,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл.сержант
 гр.защиты</t>
@@ -8555,6 +8975,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.пожарный
 </t>
@@ -8564,6 +8985,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">спасатель</t>
     </r>
@@ -8572,6 +8994,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> сержант
 гр.защиты</t>
@@ -8591,6 +9014,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">радио-телефонист</t>
     </r>
@@ -8599,6 +9023,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл.сержант
 гр.защиты</t>
@@ -8617,6 +9042,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Командир отделения </t>
     </r>
@@ -8625,6 +9051,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант гр.защиты</t>
     </r>
@@ -8638,6 +9065,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">водитель-сотрудник</t>
     </r>
@@ -8646,6 +9074,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл.сержант
 гр.защиты</t>
@@ -8663,6 +9092,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный-спасатель </t>
     </r>
@@ -8671,6 +9101,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">мл.сержант гр.защиты</t>
     </r>
@@ -8687,6 +9118,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный-спасатель мл.сержант </t>
     </r>
@@ -8695,6 +9127,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8736,6 +9169,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">командир отделения</t>
     </r>
@@ -8744,6 +9178,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст.сержант
 </t>
@@ -8753,6 +9188,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8781,6 +9217,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст. инструктор по вождению П</t>
     </r>
@@ -8789,6 +9226,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">А старшина
 </t>
@@ -8798,6 +9236,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8830,6 +9269,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.мастер ГДЗС ст.сержант </t>
     </r>
@@ -8838,6 +9278,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8857,6 +9298,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.п</t>
     </r>
@@ -8865,6 +9307,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ожарный
 спасатель 
@@ -8884,6 +9327,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ст.п</t>
     </r>
@@ -8892,6 +9336,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ожарный </t>
     </r>
@@ -8900,6 +9345,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">спасатель сержант
 </t>
@@ -8909,6 +9355,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -8919,6 +9366,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Таубаев Жа</t>
     </r>
@@ -8927,6 +9375,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">нібек Жалелұлы</t>
     </r>
@@ -8937,6 +9386,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">20</t>
     </r>
@@ -8945,6 +9395,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.01.1993</t>
     </r>
@@ -8963,6 +9414,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">29</t>
     </r>
@@ -8971,6 +9423,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.03.1993</t>
     </r>
@@ -8984,6 +9437,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">радиотелефонист</t>
     </r>
@@ -8992,6 +9446,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> мл.сержант
 </t>
@@ -9001,6 +9456,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">гр.защиты</t>
     </r>
@@ -9086,6 +9542,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Водитель сотрудник
  </t>
@@ -9095,6 +9552,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">рядовой г/з</t>
     </r>
@@ -9121,6 +9579,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Пожарный-спасатель
  </t>
@@ -9130,6 +9589,7 @@
         <sz val="14"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">рядовой г/з</t>
     </r>
@@ -9297,6 +9757,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старший лейтенант
  </t>
@@ -9306,6 +9767,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">врач </t>
     </r>
@@ -9460,6 +9922,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Абитов </t>
     </r>
@@ -9468,6 +9931,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Чингиз</t>
     </r>
@@ -9476,6 +9940,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> Се</t>
     </r>
@@ -9484,6 +9949,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">рик</t>
     </r>
@@ -9492,6 +9958,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ович</t>
     </r>
@@ -9616,6 +10083,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Қ</t>
     </r>
@@ -9624,6 +10092,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">уанышбаев Алмаз Аскар</t>
     </r>
@@ -9632,6 +10101,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ұ</t>
     </r>
@@ -9640,6 +10110,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лы</t>
     </r>
@@ -9743,6 +10214,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">майор </t>
     </r>
@@ -9751,6 +10223,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">начальник части</t>
     </r>
@@ -9767,6 +10240,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старший </t>
     </r>
@@ -9775,6 +10249,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лейтенант зам.</t>
     </r>
@@ -9783,6 +10258,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">начальник </t>
     </r>
@@ -9791,6 +10267,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">по службе</t>
     </r>
@@ -9807,6 +10284,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Подполковник </t>
     </r>
@@ -9815,6 +10293,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">зам.</t>
     </r>
@@ -9823,6 +10302,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">начальник </t>
     </r>
@@ -9831,6 +10311,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">по В и СПР</t>
     </r>
@@ -9895,6 +10376,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">младший</t>
     </r>
@@ -9903,6 +10385,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -9911,6 +10394,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -9919,6 +10403,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> пожарный</t>
     </r>
@@ -9935,6 +10420,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">младший сержант</t>
     </r>
@@ -9943,6 +10429,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> пожарный</t>
     </r>
@@ -9968,6 +10455,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">прапорщик</t>
     </r>
@@ -9976,6 +10464,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст</t>
     </r>
@@ -9984,6 +10473,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -9992,6 +10482,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по ВПМ</t>
     </r>
@@ -10008,6 +10499,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -10016,6 +10508,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст</t>
     </r>
@@ -10024,6 +10517,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -10032,6 +10526,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по ВПМ</t>
     </r>
@@ -10048,6 +10543,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">младший сержант</t>
     </r>
@@ -10056,6 +10552,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> водитель</t>
     </r>
@@ -10064,6 +10561,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-сотрудник</t>
     </r>
@@ -10080,6 +10578,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">младший сержант</t>
     </r>
@@ -10088,6 +10587,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> водитель- сотрудник</t>
     </r>
@@ -10113,6 +10613,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Кабулов Асхат</t>
     </r>
@@ -10121,6 +10622,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
@@ -10129,6 +10631,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Абдукаримович</t>
     </r>
@@ -10169,6 +10672,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">рядовой</t>
     </r>
@@ -10177,6 +10681,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> пожарный</t>
     </r>
@@ -10217,6 +10722,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -10225,6 +10731,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> водитель-сотрудник</t>
     </r>
@@ -10241,6 +10748,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -10249,6 +10757,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> водитель</t>
     </r>
@@ -10257,6 +10766,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-сотрудник</t>
     </r>
@@ -10288,6 +10798,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант</t>
     </r>
@@ -10296,6 +10807,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> командир отделения</t>
     </r>
@@ -10312,6 +10824,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Старший сержант</t>
     </r>
@@ -10320,6 +10833,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> командир отделения</t>
     </r>
@@ -10363,6 +10877,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ст.сержант</t>
     </r>
@@ -10371,6 +10886,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ст</t>
     </r>
@@ -10379,6 +10895,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -10387,6 +10904,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по</t>
     </r>
@@ -10395,6 +10913,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ВПМ</t>
     </r>
@@ -10411,6 +10930,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старшина ст</t>
     </r>
@@ -10419,6 +10939,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -10427,6 +10948,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по ВПМ</t>
     </r>
@@ -10443,6 +10965,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант водитель</t>
     </r>
@@ -10451,6 +10974,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-сотрудник</t>
     </r>
@@ -10464,6 +10988,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">23.09.1995 г</t>
     </r>
@@ -10472,6 +10997,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -10494,6 +11020,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">лейтенант</t>
     </r>
@@ -10502,6 +11029,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> начальник караула</t>
     </r>
@@ -10518,6 +11046,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Старшина</t>
     </r>
@@ -10526,6 +11055,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> командир отделения</t>
     </r>
@@ -10542,6 +11072,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старшина</t>
     </r>
@@ -10550,6 +11081,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> командир отделения</t>
     </r>
@@ -10566,6 +11098,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">сержант старший </t>
     </r>
@@ -10574,6 +11107,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный</t>
     </r>
@@ -10590,6 +11124,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">прапорщик старший </t>
     </r>
@@ -10598,6 +11133,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный</t>
     </r>
@@ -10614,6 +11150,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Сержант </t>
     </r>
@@ -10622,6 +11159,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старший </t>
     </r>
@@ -10630,6 +11168,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">пожарный</t>
     </r>
@@ -10655,6 +11194,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Мл. сержант</t>
     </r>
@@ -10663,6 +11203,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> пожарный</t>
     </r>
@@ -10679,6 +11220,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Мл.сержант</t>
     </r>
@@ -10687,6 +11229,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> пожарный</t>
     </r>
@@ -10709,6 +11252,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">старшина ст</t>
     </r>
@@ -10717,6 +11261,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">.</t>
     </r>
@@ -10725,6 +11270,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">инструктор по</t>
     </r>
@@ -10733,6 +11279,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> ВПМ</t>
     </r>
@@ -10755,6 +11302,7 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Старший сержант водитель</t>
     </r>
@@ -10763,6 +11311,7 @@
         <sz val="12"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">-сотрудник</t>
     </r>
@@ -10781,6 +11330,371 @@
   </si>
   <si>
     <t xml:space="preserve">Старшина техник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ПЧ-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Толендиев Берикжан Маулетханович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">майор г/з начальник</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Касенов Еркебулан Толеугазиевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">майор г/з зам.начальника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Искаков Сабит Муратбекович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">подполковник г/з зам.начальника</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Рахатова Людмила Абдирамановна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">подполковник г/з ст.инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Акиев Азизжан Акиевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">майор г/з ст.инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алимтаева  Айгуль  Сеильевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Амангельдиева Жанат Дженисовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кушербаева  Маржан  Саркитбаевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сагандыкова Каиргуль Кошмухамбетовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шелестова Наталья  Валерьевна </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сихимбаева Гульвира Жолдасбековна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Казиева Эльмира Толепбековна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">капитан г/з ст.инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кобдыков Талгат Джолдасович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ст. лейтенант г/з ст.инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мессершмидт Татьяна Владимировна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">майор г/з инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Худайбердиев Султан Бабамуратович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Карсенова Айман Шинадильевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Алтебаева Актыныс Алтебаевна</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Тем</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">іржан</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve"> Максат </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Муратұлы</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">капитан г/з инженер</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ы</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">нтыкбаева Айгуль Муханбетовна</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Жораева Лейла Мусаевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Канкожаева Эльмира Кунторекызы</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Изизова Н</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">урия Сельмахуновна</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">капитан г/з  инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шонгалова Гульсая Маратовна</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Калжапбар Нуржан Асылхан</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ұлы</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">ст. лейтенант г/з инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Турысбеков Абылай Дуисенгожаулы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ст.лейтенант г/з инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Асылбеков Талгат Асылбекович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Курманбаев Сункар Абдихадирович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Умбетьярова Асель Канатовна </t>
+  </si>
+  <si>
+    <t xml:space="preserve">лейтенант г.з. инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Худайбердиева Лейла Бабамуратовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">лейтенант г/з инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Саугамбаева Данара Кенсабовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Абдимомынова Арайлым Манасовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нурсапаров Абзал Ерболулы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Акильбекова Зарина Естаевна</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Иманберл</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">і Ержан Асқарұлы</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ө</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">м</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">і</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">рза</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">қ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ов Елдос Ержан</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ұ</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">лы</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">стажер(испыт срок) инженер</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Абиров Жасулан Баукеевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зунунов Расул Хетахунович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Катжанова Лаура Муратовна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Габбасова Асель Жетесбаевна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хакбердиева Асия Шавкаткызы</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Турысбекова Асем Абдулхамит</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">қызы</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Курманова Айгерим Курмановна</t>
   </si>
 </sst>
 </file>
@@ -10790,11 +11704,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -10816,96 +11731,113 @@
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="11"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Times New Roman KZ"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman KZ"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman KZ"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="14"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -10913,46 +11845,68 @@
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10.5"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF00B050"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00000A"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="18"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -10969,7 +11923,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -11072,6 +12026,13 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="hair"/>
+      <right style="hair"/>
+      <top style="hair"/>
+      <bottom style="hair"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -11098,7 +12059,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="80">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11391,6 +12352,34 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
@@ -11468,14 +12457,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E965"/>
+  <dimension ref="A1:E1007"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="48.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="25.06"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1025" min="6" style="0" width="11.52"/>
   </cols>
   <sheetData>
@@ -24367,6 +25356,552 @@
       <c r="D965" s="44" t="s">
         <v>2088</v>
       </c>
+    </row>
+    <row r="966" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A966" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B966" s="74" t="s">
+        <v>2090</v>
+      </c>
+      <c r="C966" s="75"/>
+      <c r="D966" s="74" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E966" s="76"/>
+    </row>
+    <row r="967" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A967" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B967" s="74" t="s">
+        <v>2092</v>
+      </c>
+      <c r="C967" s="75"/>
+      <c r="D967" s="74" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E967" s="76"/>
+    </row>
+    <row r="968" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A968" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B968" s="74" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C968" s="75"/>
+      <c r="D968" s="74" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E968" s="76"/>
+    </row>
+    <row r="969" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A969" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B969" s="74" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C969" s="75"/>
+      <c r="D969" s="74" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E969" s="76"/>
+    </row>
+    <row r="970" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A970" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B970" s="74" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C970" s="75"/>
+      <c r="D970" s="77" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E970" s="6"/>
+    </row>
+    <row r="971" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A971" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B971" s="74" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C971" s="75"/>
+      <c r="D971" s="74" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E971" s="76"/>
+    </row>
+    <row r="972" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A972" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B972" s="74" t="s">
+        <v>2101</v>
+      </c>
+      <c r="C972" s="75"/>
+      <c r="D972" s="74" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E972" s="76"/>
+    </row>
+    <row r="973" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A973" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B973" s="74" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C973" s="75"/>
+      <c r="D973" s="74" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E973" s="76"/>
+    </row>
+    <row r="974" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A974" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B974" s="74" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C974" s="75"/>
+      <c r="D974" s="74" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E974" s="76"/>
+    </row>
+    <row r="975" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A975" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B975" s="74" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C975" s="75"/>
+      <c r="D975" s="74" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E975" s="6"/>
+    </row>
+    <row r="976" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A976" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B976" s="74" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C976" s="75"/>
+      <c r="D976" s="77" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E976" s="76"/>
+    </row>
+    <row r="977" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A977" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B977" s="74" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C977" s="75"/>
+      <c r="D977" s="74" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E977" s="76"/>
+    </row>
+    <row r="978" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A978" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B978" s="74" t="s">
+        <v>2108</v>
+      </c>
+      <c r="C978" s="75"/>
+      <c r="D978" s="74" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E978" s="76"/>
+    </row>
+    <row r="979" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A979" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B979" s="74" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C979" s="75"/>
+      <c r="D979" s="77" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E979" s="76"/>
+    </row>
+    <row r="980" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A980" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B980" s="74" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C980" s="75"/>
+      <c r="D980" s="74" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E980" s="76"/>
+    </row>
+    <row r="981" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A981" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B981" s="74" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C981" s="75"/>
+      <c r="D981" s="77" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E981" s="76"/>
+    </row>
+    <row r="982" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A982" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B982" s="74" t="s">
+        <v>2114</v>
+      </c>
+      <c r="C982" s="75"/>
+      <c r="D982" s="74" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E982" s="76"/>
+    </row>
+    <row r="983" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A983" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B983" s="77" t="s">
+        <v>2115</v>
+      </c>
+      <c r="C983" s="75"/>
+      <c r="D983" s="74" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E983" s="76"/>
+    </row>
+    <row r="984" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A984" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B984" s="77" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C984" s="75"/>
+      <c r="D984" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E984" s="76"/>
+    </row>
+    <row r="985" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A985" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B985" s="74" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C985" s="75"/>
+      <c r="D985" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E985" s="76"/>
+    </row>
+    <row r="986" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A986" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B986" s="74" t="s">
+        <v>2119</v>
+      </c>
+      <c r="C986" s="75"/>
+      <c r="D986" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E986" s="76"/>
+    </row>
+    <row r="987" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A987" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B987" s="78" t="s">
+        <v>2120</v>
+      </c>
+      <c r="C987" s="75"/>
+      <c r="D987" s="77" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E987" s="76"/>
+    </row>
+    <row r="988" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A988" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B988" s="79" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C988" s="75"/>
+      <c r="D988" s="74" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E988" s="76"/>
+    </row>
+    <row r="989" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A989" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B989" s="77" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C989" s="75"/>
+      <c r="D989" s="74" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E989" s="76"/>
+    </row>
+    <row r="990" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A990" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B990" s="74" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C990" s="75"/>
+      <c r="D990" s="74" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E990" s="76"/>
+    </row>
+    <row r="991" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A991" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B991" s="74" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C991" s="75"/>
+      <c r="D991" s="74" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E991" s="76"/>
+    </row>
+    <row r="992" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A992" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B992" s="74" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C992" s="75"/>
+      <c r="D992" s="74" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E992" s="76"/>
+    </row>
+    <row r="993" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A993" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B993" s="74" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C993" s="75"/>
+      <c r="D993" s="74" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E993" s="76"/>
+    </row>
+    <row r="994" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A994" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B994" s="74" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C994" s="75"/>
+      <c r="D994" s="74" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E994" s="76"/>
+    </row>
+    <row r="995" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A995" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B995" s="74" t="s">
+        <v>2133</v>
+      </c>
+      <c r="C995" s="75"/>
+      <c r="D995" s="74" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E995" s="76"/>
+    </row>
+    <row r="996" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A996" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B996" s="74" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C996" s="75"/>
+      <c r="D996" s="74" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E996" s="76"/>
+    </row>
+    <row r="997" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A997" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B997" s="74" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C997" s="75"/>
+      <c r="D997" s="74" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E997" s="76"/>
+    </row>
+    <row r="998" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A998" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B998" s="79" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C998" s="75"/>
+      <c r="D998" s="74" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E998" s="76"/>
+    </row>
+    <row r="999" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A999" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B999" s="77" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C999" s="75"/>
+      <c r="D999" s="74" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E999" s="76"/>
+    </row>
+    <row r="1000" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1000" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1000" s="78" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C1000" s="75"/>
+      <c r="D1000" s="74" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1000" s="76"/>
+    </row>
+    <row r="1001" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1001" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1001" s="74" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C1001" s="75"/>
+      <c r="D1001" s="74" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1001" s="76"/>
+    </row>
+    <row r="1002" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1002" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1002" s="74" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C1002" s="75"/>
+      <c r="D1002" s="74" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E1002" s="76"/>
+    </row>
+    <row r="1003" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1003" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1003" s="74" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C1003" s="75"/>
+      <c r="D1003" s="74" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1003" s="76"/>
+    </row>
+    <row r="1004" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1004" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1004" s="74" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C1004" s="75"/>
+      <c r="D1004" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1004" s="76"/>
+    </row>
+    <row r="1005" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1005" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1005" s="74" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C1005" s="75"/>
+      <c r="D1005" s="74" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1005" s="76"/>
+    </row>
+    <row r="1006" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1006" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1006" s="77" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C1006" s="75"/>
+      <c r="D1006" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1006" s="76"/>
+    </row>
+    <row r="1007" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1007" s="73" t="s">
+        <v>2089</v>
+      </c>
+      <c r="B1007" s="74" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C1007" s="75"/>
+      <c r="D1007" s="77" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E1007" s="76"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/database/seeds/sources/staff.xlsx
+++ b/database/seeds/sources/staff.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="2147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3647" uniqueCount="2181">
   <si>
     <t xml:space="preserve">ПЧ</t>
   </si>
@@ -11695,6 +11695,140 @@
   </si>
   <si>
     <t xml:space="preserve">Курманова Айгерим Курмановна</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Даус Валерий Арнольдович</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Подполковник, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Оперативный дежурный</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Жаманкулов Аскар Нуржанович</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Майор, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Заместитель ОД</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Турсумбаев Бекжан Айтбекович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">старший лейтенант, Помощник ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кудеринов Дастан Серикович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Старшина, Специалист водитель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тулпар-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ярцев Денис Николаевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Майор,Оперативный дежурный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тетроев Руслан Сахрабович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Майор, Заместитель ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мырзагалиев Жандос Рашитович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Попов Александр Юрьевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Прапорщик, Специалист водитель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ганиев Пулат Муратович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитан, оперативный дежурный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ешмухамбетов Ерганат Талбалдиевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Майор,Заместитель ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оспанов Омар Нургалиевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Помощник ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мусике Куан Абдирулы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мусин Диас Радиевич</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Майор, Оперативный дежурный</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ахметов Мурат Маратович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Капитан, Заместитель ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанаев Рахимжан Бакытжанович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оспанов Самат Куатович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Младший сержант, Специалист водитель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Кияткин Антон Павлович</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подполковник, Заместитель ОД</t>
+  </si>
+  <si>
+    <t xml:space="preserve">410-411</t>
   </si>
 </sst>
 </file>
@@ -11704,7 +11838,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -11908,6 +12042,11 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -12059,7 +12198,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="82">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -12380,6 +12519,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="false"/>
@@ -12457,7 +12604,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E1007"/>
+  <dimension ref="A1:E1024"/>
   <sheetFormatPr defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.45"/>
@@ -25903,6 +26050,261 @@
       </c>
       <c r="E1007" s="76"/>
     </row>
+    <row r="1008" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1008" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1008" s="74" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C1008" s="80"/>
+      <c r="D1008" s="81" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E1008" s="80" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1009" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1009" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1009" s="74" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C1009" s="80"/>
+      <c r="D1009" s="81" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E1009" s="80" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1010" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1010" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1010" s="74" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C1010" s="74"/>
+      <c r="D1010" s="80" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1010" s="80" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1011" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1011" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1011" s="74" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C1011" s="80"/>
+      <c r="D1011" s="80" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1011" s="80" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="1012" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1012" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1012" s="74" t="s">
+        <v>2157</v>
+      </c>
+      <c r="C1012" s="80"/>
+      <c r="D1012" s="80" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E1012" s="80" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1013" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1013" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1013" s="74" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C1013" s="80"/>
+      <c r="D1013" s="80" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E1013" s="80" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1014" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1014" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1014" s="74" t="s">
+        <v>2161</v>
+      </c>
+      <c r="C1014" s="80"/>
+      <c r="D1014" s="80" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1014" s="80" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1015" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1015" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1015" s="74" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C1015" s="80"/>
+      <c r="D1015" s="80" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E1015" s="80" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="1016" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1016" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1016" s="74" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C1016" s="80"/>
+      <c r="D1016" s="80" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E1016" s="80" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1017" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1017" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1017" s="74" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C1017" s="80"/>
+      <c r="D1017" s="80" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E1017" s="80" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1018" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1018" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1018" s="74" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C1018" s="80"/>
+      <c r="D1018" s="80" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E1018" s="80" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1019" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1019" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1019" s="74" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C1019" s="80"/>
+      <c r="D1019" s="80" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E1019" s="80" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="1020" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1020" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1020" s="74" t="s">
+        <v>2171</v>
+      </c>
+      <c r="C1020" s="80"/>
+      <c r="D1020" s="80" t="s">
+        <v>2172</v>
+      </c>
+      <c r="E1020" s="80" t="n">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="1021" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1021" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1021" s="74" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C1021" s="80"/>
+      <c r="D1021" s="80" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E1021" s="80" t="n">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="1022" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1022" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1022" s="74" t="s">
+        <v>2175</v>
+      </c>
+      <c r="C1022" s="80"/>
+      <c r="D1022" s="80" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E1022" s="80" t="n">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="1023" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1023" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1023" s="74" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C1023" s="80"/>
+      <c r="D1023" s="80" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E1023" s="80" t="s">
+        <v>2156</v>
+      </c>
+    </row>
+    <row r="1024" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1024" s="0" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B1024" s="74" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C1024" s="80"/>
+      <c r="D1024" s="80" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E1024" s="80" t="s">
+        <v>2180</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
